--- a/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
@@ -29,12 +29,30 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
+        <bgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -50,14 +68,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
-        <bgColor rgb="00EEEEEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-        <bgColor rgb="00D9D2E9"/>
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,20 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
+        <fgColor rgb="00EEEEEE"/>
+        <bgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAD1DC"/>
         <bgColor rgb="00EAD1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,6 +139,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -500,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -521,183 +530,175 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>254941</v>
+        <v>243569</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>40623</v>
+        <v>40055</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>254715</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>40623</v>
+        <v>252298</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>254556</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>40623</v>
+        <v>252519</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>254910</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>406372</v>
+        <v>252680</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>254915</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252209</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>254758</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252210</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>254117</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>243536</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>254512</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>406232</v>
+        <v>243526</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>254519</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>406422</v>
+        <v>243535</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>254256</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>406422</v>
+        <v>252220</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>254375</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>40624</v>
+        <v>244023</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>254187</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>406372</v>
+        <v>252456</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>40049</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>254245</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252549</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>254521</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252336</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>254106</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252467</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>253885</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252790</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>254129</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>40623</v>
+        <v>252755</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>254291</v>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>40624</v>
+        <v>252334</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>252061</v>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>40628</v>
+        <v>252665</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>254293</v>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>40624</v>
+        <v>252426</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>253865</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+        <v>252470</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -705,9 +706,9 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>254451</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+        <v>252899</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -715,241 +716,233 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>254555</v>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>406232</v>
+        <v>252576</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>253650</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>251919</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>254652</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252245</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>254714</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>40623</v>
+        <v>252686</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>253382</v>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>406372</v>
+        <v>252547</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>243569</v>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>406372</v>
+        <v>251926</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>255039</v>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>40624</v>
+        <v>251495</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>254824</v>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>406232</v>
+        <v>250284</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>254599</v>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>406372</v>
+        <v>252207</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>254356</v>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>406372</v>
+        <v>252723</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>253961</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>406372</v>
+        <v>251790</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>254101</v>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>406552</v>
+        <v>252378</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>253974</v>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>406552</v>
+        <v>252362</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>254100</v>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>406552</v>
+        <v>252350</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>254354</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252473</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>254252</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252598</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>254339</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252656</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>254547</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252662</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>254419</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>235572</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>40055</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>253906</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>251685</v>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>254481</v>
-      </c>
-      <c r="B44" s="8" t="n">
-        <v>40642</v>
+        <v>252476</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>254762</v>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>40623</v>
+        <v>252713</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>253380</v>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>40606</v>
+        <v>252414</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>255043</v>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>406422</v>
+        <v>252201</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>40055</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>254433</v>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>406422</v>
+        <v>252371</v>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>254189</v>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>406422</v>
+        <v>245089</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>254230</v>
-      </c>
-      <c r="B50" s="6" t="n">
-        <v>406422</v>
+        <v>252369</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>254460</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+        <v>245623</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -957,107 +950,101 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>254287</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252978</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>40049</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>254574</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>251849</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>40042 (esterno)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>254598</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>243527</v>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>253694</v>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>40623</v>
+        <v>243523</v>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>253897</v>
+        <v>252495</v>
       </c>
       <c r="B56" s="8" t="n">
-        <v>40606</v>
+        <v>301</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>254283</v>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>406372</v>
+        <v>252890</v>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>244023</v>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>406062</v>
+        <v>252085</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>307</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>254651</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252087</v>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>307</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>254893</v>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>406372</v>
+        <v>252364</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>254586</v>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>406372</v>
+        <v>252638</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>254237</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
+        <v>252783</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>253838</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
+        <v>252157</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1065,9 +1052,9 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>254107</v>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
+        <v>252507</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1075,87 +1062,85 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>254381</v>
-      </c>
-      <c r="B65" s="6" t="n">
-        <v>406422</v>
+        <v>252511</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>254713</v>
+        <v>252999</v>
       </c>
       <c r="B66" s="3" t="n">
-        <v>40623</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>254156</v>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>40606</v>
+        <v>251812</v>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>254165</v>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>40606</v>
+        <v>250383</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>254198</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252814</v>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>309</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>254309</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252785</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>254429</v>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>406372</v>
+        <v>252784</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>235572</v>
-      </c>
-      <c r="B72" s="4" t="n">
-        <v>406372</v>
+        <v>251231</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>40034 (esterno)</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>254605</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252277</v>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>40024</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>254653</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
+        <v>252517</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1163,187 +1148,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>254276</v>
-      </c>
-      <c r="B75" s="6" t="n">
-        <v>406422</v>
+        <v>252778</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>253614</v>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>254385</v>
-      </c>
-      <c r="B77" s="9" t="n">
-        <v>40627</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>254546</v>
-      </c>
-      <c r="B78" s="7" t="n">
-        <v>406242</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>254675</v>
-      </c>
-      <c r="B79" s="6" t="n">
-        <v>406422</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>254188</v>
-      </c>
-      <c r="B80" s="4" t="n">
-        <v>406372</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>254437</v>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>406372</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>254903</v>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>254756</v>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>250284</v>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>252811</v>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>254365</v>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>254457</v>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v>406372</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>254166</v>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>406372</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>254609</v>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>40655</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>252980</v>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>254427</v>
-      </c>
-      <c r="B91" s="8" t="n">
-        <v>40649</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>254428</v>
-      </c>
-      <c r="B92" s="8" t="n">
-        <v>40649</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>254173</v>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>254967</v>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>254671</v>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
+        <v>252779</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
@@ -38,20 +38,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-        <bgColor rgb="00D9D2E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D5E8D4"/>
         <bgColor rgb="00D5E8D4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,8 +56,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00D9D2E9"/>
+        <bgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,8 +86,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD1DC"/>
-        <bgColor rgb="00EAD1DC"/>
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -530,355 +530,353 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>243569</v>
+        <v>252207</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>40055</v>
+        <v>240050</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>252298</v>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>302</v>
+        <v>252723</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>252519</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>240055</v>
+        <v>252890</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>252680</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>240046</v>
+        <v>252371</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>252209</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>240050</v>
+        <v>243527</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>252210</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>240050</v>
+        <v>243523</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>243536</v>
-      </c>
-      <c r="B8" s="8" t="n">
+        <v>251790</v>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>243526</v>
-      </c>
-      <c r="B9" s="8" t="n">
+        <v>243536</v>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>301</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>243535</v>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>301</v>
+        <v>243526</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>252220</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>240050</v>
+        <v>243535</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>244023</v>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>240054</v>
+        <v>252680</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>252456</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>40049</v>
+        <v>252210</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>252549</v>
-      </c>
-      <c r="B14" s="7" t="n">
+        <v>252209</v>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>240050</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>252336</v>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>240049</v>
+        <v>252814</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>309</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>252467</v>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>240049</v>
+        <v>252519</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>252790</v>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>240049</v>
+        <v>252495</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>252755</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>302</v>
+        <v>252201</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>252334</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>243569</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>40055</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>252665</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252978</v>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>40049</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>252426</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252298</v>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>252470</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252378</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>252899</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252362</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>252576</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>251812</v>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>251919</v>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>302</v>
+        <v>250383</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>252245</v>
+        <v>252369</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>240046</v>
+        <v>240055</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>252686</v>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>310</v>
+        <v>250284</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>252547</v>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>240050</v>
+        <v>252783</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>251926</v>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>240049</v>
+        <v>252784</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>251495</v>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>240049</v>
+        <v>252785</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>250284</v>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>240050</v>
+        <v>235572</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>252207</v>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>240050</v>
+        <v>251685</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>252723</v>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>240050</v>
+        <v>252456</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>251790</v>
-      </c>
-      <c r="B34" s="6" t="n">
+        <v>244023</v>
+      </c>
+      <c r="B34" s="4" t="n">
         <v>240054</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>252378</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>240055</v>
+        <v>252467</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>252362</v>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>240055</v>
+        <v>252790</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>252350</v>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>240055</v>
+        <v>252336</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>252473</v>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>240055</v>
+        <v>252755</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>252598</v>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>240055</v>
+        <v>252087</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>252656</v>
+        <v>252350</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>240055</v>
+        <v>40055</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>252662</v>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>240055</v>
+        <v>252598</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>235572</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>40055</v>
+        <v>252662</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>251685</v>
-      </c>
-      <c r="B43" s="8" t="n">
-        <v>301</v>
+        <v>252426</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>252476</v>
+        <v>252473</v>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
@@ -888,15 +886,17 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>252713</v>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>302</v>
+        <v>252656</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>252414</v>
+        <v>252899</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
@@ -906,23 +906,27 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>252201</v>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>40055</v>
+        <v>252476</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>252371</v>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>240050</v>
+        <v>252364</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>245089</v>
+        <v>252547</v>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
@@ -932,15 +936,17 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>252369</v>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>240055</v>
+        <v>251231</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>40034 (esterno)</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>245623</v>
+        <v>252334</v>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
@@ -950,73 +956,85 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>252978</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>40049</v>
+        <v>252470</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>251849</v>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>40042 (esterno)</t>
+        <v>252549</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>243527</v>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>301</v>
+        <v>252665</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>243523</v>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>301</v>
+        <v>252277</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>40024</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>252495</v>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>301</v>
+        <v>252085</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>252890</v>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>301</v>
+        <v>251849</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>40042 (esterno)</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>252085</v>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>307</v>
+        <v>252220</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>252087</v>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>307</v>
+        <v>251495</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>252364</v>
+        <v>252157</v>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
@@ -1026,43 +1044,39 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>252638</v>
-      </c>
-      <c r="B61" s="3" t="n">
+        <v>252999</v>
+      </c>
+      <c r="B61" s="5" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>252783</v>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>303</v>
+        <v>252713</v>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>252157</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>251926</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>252507</v>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252638</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>252511</v>
+        <v>252414</v>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
@@ -1072,68 +1086,76 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>252999</v>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>303</v>
+        <v>252507</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>251812</v>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>302</v>
+        <v>252511</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>250383</v>
-      </c>
-      <c r="B68" s="5" t="n">
-        <v>240055</v>
+        <v>245089</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>252814</v>
-      </c>
-      <c r="B69" s="11" t="n">
-        <v>309</v>
+        <v>251919</v>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>252785</v>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>303</v>
+        <v>252245</v>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>252784</v>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>303</v>
+        <v>252686</v>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>251231</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>40034 (esterno)</t>
+        <v>245623</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>252277</v>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>40024</v>
+        <v>252778</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -1148,7 +1170,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>252778</v>
+        <v>252779</v>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
@@ -1158,7 +1180,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>252779</v>
+        <v>252576</v>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>

--- a/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
@@ -38,14 +38,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00CCE5FF"/>
+        <bgColor rgb="00CCE5FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CCE5FF"/>
-        <bgColor rgb="00CCE5FF"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -56,26 +68,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-        <bgColor rgb="00D9D2E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EAD1DC"/>
         <bgColor rgb="00EAD1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,8 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00D9D2E9"/>
+        <bgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
   </fills>
@@ -530,7 +530,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>252207</v>
+        <v>252723</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>240050</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>252723</v>
+        <v>252207</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>240050</v>
@@ -546,15 +546,15 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>252890</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>240054</v>
+        <v>252680</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>252371</v>
+        <v>252210</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>240050</v>
@@ -562,353 +562,357 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>243527</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>240054</v>
+        <v>252209</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>243523</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>240054</v>
+        <v>252371</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>251790</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>301</v>
+        <v>243569</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>243536</v>
+        <v>252814</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>243526</v>
+        <v>252362</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>240054</v>
+        <v>240055</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>243535</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>301</v>
+        <v>252378</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>252680</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>240050</v>
+        <v>252298</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>252210</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>240050</v>
+        <v>250383</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>252209</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>240050</v>
+        <v>252495</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>252814</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>309</v>
+        <v>252519</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>252519</v>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>240055</v>
+        <v>252890</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>252495</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>301</v>
+        <v>251812</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>252201</v>
-      </c>
-      <c r="B18" s="6" t="n">
+        <v>252369</v>
+      </c>
+      <c r="B18" s="4" t="n">
         <v>240055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>243569</v>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>40055</v>
+        <v>250284</v>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>252978</v>
+        <v>252783</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>40049</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>252298</v>
+        <v>252467</v>
       </c>
       <c r="B21" s="8" t="n">
-        <v>302</v>
+        <v>240046</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>252378</v>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>240055</v>
+        <v>252476</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>252362</v>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>240055</v>
+        <v>252665</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>251812</v>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>302</v>
+        <v>252277</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>40024</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>250383</v>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>240055</v>
+        <v>252350</v>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>40055</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>252369</v>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>240055</v>
+        <v>252598</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>250284</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>240050</v>
+        <v>252576</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>252783</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>303</v>
+        <v>252779</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>252784</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>303</v>
+        <v>252899</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>252785</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>303</v>
+        <v>252426</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>235572</v>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>240055</v>
+        <v>252778</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>251685</v>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>301</v>
+        <v>252157</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>252456</v>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>240049</v>
+        <v>252201</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>40055</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>244023</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>240054</v>
+        <v>252999</v>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>252467</v>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>240046</v>
+        <v>252087</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>307</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>252790</v>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>240049</v>
+        <v>251849</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>40042 (esterno)</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>252336</v>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>240049</v>
+        <v>252220</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>252755</v>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>235572</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>240055</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>252087</v>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>244023</v>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>252350</v>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>40055</v>
+        <v>252638</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>303</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>252598</v>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252085</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>307</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>252662</v>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252549</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>240050</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>252426</v>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252662</v>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>252473</v>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252656</v>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>252656</v>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252473</v>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>252899</v>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252790</v>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>252476</v>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
+        <v>252336</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -918,7 +922,7 @@
       <c r="A48" s="2" t="n">
         <v>252364</v>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -926,9 +930,9 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>252547</v>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
+        <v>252470</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -936,87 +940,77 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>251231</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>40034 (esterno)</t>
+        <v>252334</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>252334</v>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252713</v>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>252470</v>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252456</v>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>40049</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>252549</v>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252755</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>252665</v>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>251495</v>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>252277</v>
-      </c>
-      <c r="B55" s="6" t="n">
-        <v>40024</v>
+        <v>251926</v>
+      </c>
+      <c r="B55" s="10" t="n">
+        <v>240049</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>252085</v>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252414</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>251849</v>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>40042 (esterno)</t>
+        <v>252511</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>252220</v>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
+        <v>252507</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1024,91 +1018,81 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>251495</v>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252978</v>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>40049</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>252157</v>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>251919</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>252999</v>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>303</v>
+        <v>252245</v>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>240046</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>252713</v>
-      </c>
-      <c r="B62" s="8" t="n">
-        <v>302</v>
+        <v>252686</v>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>251926</v>
-      </c>
-      <c r="B63" s="6" t="n">
-        <v>240049</v>
+        <v>243536</v>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>252638</v>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>303</v>
+        <v>243523</v>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>240054</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>252414</v>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>243535</v>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>252507</v>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>243526</v>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>252511</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>243527</v>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
         <v>245089</v>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1116,63 +1100,61 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>251919</v>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>302</v>
+        <v>245623</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>252245</v>
-      </c>
-      <c r="B70" s="9" t="n">
-        <v>240046</v>
+        <v>251790</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>40054</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>252686</v>
-      </c>
-      <c r="B71" s="6" t="n">
-        <v>310</v>
+        <v>252784</v>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>40055</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>245623</v>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>252785</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>40055</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>252778</v>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>251231</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>40034 (esterno)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>252517</v>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>251685</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>40054</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>252779</v>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
+        <v>252547</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1180,9 +1162,9 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>252576</v>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
+        <v>252517</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
         <bgColor rgb="00FCE5CD"/>
       </patternFill>
@@ -68,26 +62,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD1DC"/>
-        <bgColor rgb="00EAD1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEEEEE"/>
         <bgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-        <bgColor rgb="00D9D2E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,15 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -509,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -530,205 +503,219 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>252723</v>
+        <v>255699</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>240050</v>
+        <v>40987</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>252207</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>240050</v>
+        <v>255672</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>40968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>252680</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>240050</v>
+        <v>255072</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>40999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>252210</v>
+        <v>255047</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>240050</v>
+        <v>40987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>252209</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>240050</v>
+        <v>255534</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>252371</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>240050</v>
+        <v>255244</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>243569</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>240055</v>
+        <v>255334</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>252814</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>309</v>
+        <v>255775</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>252362</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>240055</v>
+        <v>254061</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>252378</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>240055</v>
+        <v>260254</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>252298</v>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>302</v>
+        <v>255470</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>250383</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>240055</v>
+        <v>254779</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>252495</v>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>240054</v>
+        <v>255292</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>252519</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>240055</v>
+        <v>254067</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>252890</v>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>240054</v>
+        <v>254685</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>251812</v>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>302</v>
+        <v>255593</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>252369</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>240055</v>
+        <v>255596</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>250284</v>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>240046</v>
+        <v>255560</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>252783</v>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>303</v>
+        <v>255667</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>252467</v>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>240046</v>
+        <v>255700</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>252476</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255354</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>40989</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>252665</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255676</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>252277</v>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>40024</v>
+        <v>255765</v>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>252350</v>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>40055</v>
+        <v>255462</v>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>252598</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+        <v>255802</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -736,9 +723,9 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>252576</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
+        <v>251077</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -746,9 +733,9 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>252779</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
+        <v>251288</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -756,9 +743,9 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>252899</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
+        <v>255397</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -766,9 +753,9 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>252426</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
+        <v>255361</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -776,9 +763,9 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>252778</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
+        <v>255275</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -786,9 +773,9 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>252157</v>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
+        <v>254914</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -796,123 +783,143 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>252201</v>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>40055</v>
+        <v>255640</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>252999</v>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>303</v>
+        <v>254666</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>252087</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>307</v>
+        <v>254788</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>251849</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>40042 (esterno)</t>
+        <v>255767</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>252220</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>240050</v>
+        <v>255762</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>235572</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>240055</v>
+        <v>255764</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>244023</v>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>240054</v>
+        <v>254363</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>252638</v>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>303</v>
+        <v>235572</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>252085</v>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>307</v>
+        <v>255353</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>252549</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>240050</v>
+        <v>244023</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>252662</v>
-      </c>
-      <c r="B43" s="8" t="n">
-        <v>240046</v>
+        <v>254460</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>252656</v>
-      </c>
-      <c r="B44" s="8" t="n">
-        <v>240046</v>
+        <v>255507</v>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>252473</v>
-      </c>
-      <c r="B45" s="8" t="n">
-        <v>240046</v>
+        <v>255256</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>252790</v>
-      </c>
-      <c r="B46" s="10" t="n">
-        <v>240049</v>
+        <v>255780</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>40968</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>252336</v>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
+        <v>255590</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -920,179 +927,195 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>252364</v>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255568</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>252470</v>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255698</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>252334</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>254622</v>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>252713</v>
-      </c>
-      <c r="B51" s="6" t="n">
-        <v>302</v>
+        <v>255441</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>252456</v>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>40049</v>
+        <v>255457</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>252755</v>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>302</v>
+        <v>254112</v>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>251495</v>
-      </c>
-      <c r="B54" s="10" t="n">
-        <v>240049</v>
+        <v>254878</v>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>251926</v>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>240049</v>
+        <v>254997</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>252414</v>
-      </c>
-      <c r="B56" s="7" t="n">
-        <v>240054</v>
+        <v>253133</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>252511</v>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255707</v>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>252507</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255696</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>252978</v>
-      </c>
-      <c r="B59" s="11" t="n">
-        <v>40049</v>
+        <v>255391</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>251919</v>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>302</v>
+        <v>252647</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>252245</v>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>240046</v>
+        <v>255673</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>252686</v>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>310</v>
+        <v>255010</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>243536</v>
-      </c>
-      <c r="B63" s="7" t="n">
-        <v>240054</v>
+        <v>255618</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>243523</v>
-      </c>
-      <c r="B64" s="7" t="n">
-        <v>240054</v>
+        <v>255617</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>243535</v>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>301</v>
+        <v>255709</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>243526</v>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>301</v>
+        <v>260215</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>243527</v>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>301</v>
+        <v>260018</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>245089</v>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
+        <v>260270</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1100,9 +1123,9 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>245623</v>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
+        <v>260153</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1110,51 +1133,59 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>251790</v>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>40054</v>
+        <v>255388</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>252784</v>
-      </c>
-      <c r="B71" s="7" t="n">
-        <v>40055</v>
+        <v>260154</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>252785</v>
-      </c>
-      <c r="B72" s="7" t="n">
-        <v>40055</v>
+        <v>254297</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>251231</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>40034 (esterno)</t>
+        <v>260023</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>251685</v>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>40054</v>
+        <v>255561</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>252547</v>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
+        <v>255637</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1162,9 +1193,499 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>252517</v>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
+        <v>260272</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>260061</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>260064</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>260070</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>255548</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>260071</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>255565</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>260046</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>255440</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>260204</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>260203</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>260063</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>260139</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>255564</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>260006</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>260062</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>254199</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>260082</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>260035</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>255796</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>255197</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>255190</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>255182</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>255799</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>255710</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>255583</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>255608</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>255482</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>253788</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>260296</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>255412</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>255411</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>260144</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>255409</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>255410</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>255008</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>260029</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>255169</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>260261</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>260065</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>255611</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>255562</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>255554</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>255546</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>255549</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>255563</v>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>255558</v>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>255557</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>255553</v>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>255555</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_veicoli.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -44,20 +44,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,6 +70,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
         <bgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
+        <bgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +121,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -503,39 +512,41 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>255699</v>
+        <v>255354</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>40987</v>
+        <v>40989</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
         <v>255672</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="3" t="n">
         <v>40968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>255072</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>40999</v>
+        <v>255699</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>255047</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>40987</v>
+        <v>255388</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>41004 (esterno)</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>255534</v>
+        <v>255568</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>40988</v>
@@ -543,35 +554,31 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>255244</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>40988</v>
+        <v>255637</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>255334</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255534</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>255775</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255611</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>254061</v>
+        <v>255775</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -581,7 +588,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>260254</v>
+        <v>260062</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -591,15 +598,17 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>255470</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>40987</v>
+        <v>255709</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>254779</v>
+        <v>255799</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -609,15 +618,17 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>255292</v>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>40991</v>
+        <v>254914</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>254067</v>
+        <v>255640</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -627,7 +638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>254685</v>
+        <v>254788</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -637,7 +648,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>255593</v>
+        <v>254363</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -647,7 +658,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>255596</v>
+        <v>235572</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -657,93 +668,99 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>255560</v>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>40988</v>
+        <v>260254</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>255667</v>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>40991</v>
+        <v>255561</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>255700</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>40987</v>
+        <v>244023</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>255354</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>40989</v>
+        <v>254460</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>255676</v>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>40991</v>
+        <v>255470</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>255765</v>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>40991</v>
+        <v>255504</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>41001 (esterno)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>255462</v>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>40991</v>
+        <v>255481</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>40993 (esterno)</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>255802</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255707</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>251077</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255765</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>251288</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255462</v>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>255397</v>
+        <v>251077</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
@@ -753,7 +770,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>255361</v>
+        <v>255275</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -763,7 +780,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>255275</v>
+        <v>255361</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -773,7 +790,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>254914</v>
+        <v>251288</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
@@ -783,141 +800,127 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>255640</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>254635</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>40981 (esterno)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>254666</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255780</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>40968</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>254788</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255700</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>255767</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255292</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>255762</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255072</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>40999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>255764</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255667</v>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>254363</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>254622</v>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>235572</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>254878</v>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>255353</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255696</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>244023</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255560</v>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>254460</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255244</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>255507</v>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>40988</v>
+        <v>260272</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>255256</v>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>40988</v>
+        <v>255802</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>255780</v>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>40968</v>
+        <v>255397</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>255590</v>
+        <v>253133</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
@@ -927,31 +930,37 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>255568</v>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>40988</v>
+        <v>260261</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>255698</v>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>40987</v>
+        <v>255440</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>254622</v>
-      </c>
-      <c r="B50" s="8" t="n">
-        <v>40991</v>
+        <v>255767</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>255441</v>
+        <v>255762</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
@@ -961,7 +970,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>255457</v>
+        <v>255764</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
@@ -971,23 +980,27 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>254112</v>
-      </c>
-      <c r="B53" s="8" t="n">
-        <v>40991</v>
+        <v>255562</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>254878</v>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>40991</v>
+        <v>255554</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>254997</v>
+        <v>255546</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
@@ -997,7 +1010,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>253133</v>
+        <v>255549</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
@@ -1007,23 +1020,27 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>255707</v>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>40991</v>
+        <v>255563</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>255696</v>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>40987</v>
+        <v>255553</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>255391</v>
+        <v>255564</v>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
@@ -1033,7 +1050,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>252647</v>
+        <v>255557</v>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
@@ -1043,7 +1060,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>255673</v>
+        <v>255558</v>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
@@ -1053,7 +1070,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>255010</v>
+        <v>255548</v>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
@@ -1063,7 +1080,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>255618</v>
+        <v>255565</v>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
@@ -1073,7 +1090,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>255617</v>
+        <v>255555</v>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
@@ -1083,7 +1100,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>255709</v>
+        <v>255353</v>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
@@ -1093,27 +1110,23 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>260215</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255507</v>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>260018</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255256</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>40988</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>260270</v>
+        <v>255596</v>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
@@ -1123,7 +1136,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>260153</v>
+        <v>255673</v>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
@@ -1133,7 +1146,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>255388</v>
+        <v>255593</v>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
@@ -1143,7 +1156,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>260154</v>
+        <v>255391</v>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
@@ -1153,17 +1166,15 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>254297</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255698</v>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>260023</v>
+        <v>252647</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
@@ -1173,7 +1184,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>255561</v>
+        <v>255618</v>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
@@ -1183,7 +1194,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>255637</v>
+        <v>254685</v>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
@@ -1193,7 +1204,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>260272</v>
+        <v>255441</v>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
@@ -1203,7 +1214,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>260061</v>
+        <v>255457</v>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
@@ -1213,47 +1224,41 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>260064</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>254112</v>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>260070</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255676</v>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>40991</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>255548</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>255047</v>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>40987</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>260071</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>243224</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>40993 (esterno)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>255565</v>
+        <v>254067</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
@@ -1263,7 +1268,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>260046</v>
+        <v>254061</v>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
@@ -1273,7 +1278,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>255440</v>
+        <v>255010</v>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
@@ -1283,7 +1288,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>260204</v>
+        <v>255617</v>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
@@ -1293,7 +1298,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>260203</v>
+        <v>254779</v>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
@@ -1303,7 +1308,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>260063</v>
+        <v>255334</v>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
@@ -1313,7 +1318,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>260139</v>
+        <v>254997</v>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
@@ -1323,7 +1328,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>255564</v>
+        <v>254666</v>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
@@ -1333,7 +1338,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>260006</v>
+        <v>255590</v>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
@@ -1343,7 +1348,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>260062</v>
+        <v>260215</v>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
@@ -1353,7 +1358,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>254199</v>
+        <v>254297</v>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
@@ -1363,7 +1368,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>260082</v>
+        <v>260153</v>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
@@ -1373,7 +1378,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>260035</v>
+        <v>260270</v>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
@@ -1383,7 +1388,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>255796</v>
+        <v>260154</v>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>255197</v>
+        <v>254199</v>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
@@ -1403,7 +1408,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>255190</v>
+        <v>260018</v>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
@@ -1413,7 +1418,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>255182</v>
+        <v>260061</v>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
@@ -1423,7 +1428,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>255799</v>
+        <v>260065</v>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
@@ -1433,7 +1438,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>255710</v>
+        <v>260063</v>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
@@ -1443,7 +1448,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>255583</v>
+        <v>260070</v>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
@@ -1453,7 +1458,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>255608</v>
+        <v>260071</v>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
@@ -1463,7 +1468,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>255482</v>
+        <v>260046</v>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
@@ -1473,7 +1478,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>253788</v>
+        <v>260204</v>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
@@ -1483,7 +1488,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>260296</v>
+        <v>260203</v>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
@@ -1493,7 +1498,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>255412</v>
+        <v>260006</v>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
@@ -1503,7 +1508,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>255411</v>
+        <v>260082</v>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
@@ -1513,7 +1518,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>260144</v>
+        <v>260023</v>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
@@ -1523,7 +1528,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>255409</v>
+        <v>260139</v>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
@@ -1533,7 +1538,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>255410</v>
+        <v>255583</v>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
@@ -1543,7 +1548,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>255008</v>
+        <v>255197</v>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
@@ -1553,7 +1558,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>260029</v>
+        <v>255182</v>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
@@ -1563,7 +1568,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>255169</v>
+        <v>255190</v>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>260261</v>
+        <v>260035</v>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
@@ -1583,7 +1588,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>260065</v>
+        <v>255796</v>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
@@ -1593,7 +1598,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>255611</v>
+        <v>255608</v>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
@@ -1603,7 +1608,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>255562</v>
+        <v>260144</v>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
@@ -1613,7 +1618,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>255554</v>
+        <v>255482</v>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
@@ -1623,7 +1628,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>255546</v>
+        <v>253788</v>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
@@ -1633,7 +1638,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>255549</v>
+        <v>260296</v>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
@@ -1643,7 +1648,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>255563</v>
+        <v>255409</v>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
@@ -1653,7 +1658,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>255558</v>
+        <v>255411</v>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
@@ -1663,7 +1668,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>255557</v>
+        <v>255412</v>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
@@ -1673,7 +1678,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>255553</v>
+        <v>255008</v>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
@@ -1683,9 +1688,49 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>255555</v>
+        <v>255410</v>
       </c>
       <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>260029</v>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>255710</v>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>260064</v>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>255169</v>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
